--- a/40_AWS/99_参考過去資料/02_設計書/POS_LVN&Cresco様 - 一般/99.作業用フォルダ/毎田/ECSの会話用.xlsx
+++ b/40_AWS/99_参考過去資料/02_設計書/POS_LVN&Cresco様 - 一般/99.作業用フォルダ/毎田/ECSの会話用.xlsx
@@ -5357,19 +5357,19 @@
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8dbf7540-46e2-4291-999e-80d6200bae7a">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="74a0992f-8328-4daf-870b-3d2b13d3e940">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d13a9ec-4dcc-4bf0-b813-bb41ddf201ec" xsi:nil="true"/>
+    <TaxCatchAll xmlns="4a37abda-15dd-4e37-8275-3b7fb2897b65" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100362C55BE5E260749AE179ACE10276E66" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a60865d5aa58f0636dceb2dd83281f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8dbf7540-46e2-4291-999e-80d6200bae7a" xmlns:ns3="2d13a9ec-4dcc-4bf0-b813-bb41ddf201ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aea82fe451e55694012912181e40c1a8" ns2:_="" ns3:_="">
-    <xsd:import namespace="8dbf7540-46e2-4291-999e-80d6200bae7a"/>
-    <xsd:import namespace="2d13a9ec-4dcc-4bf0-b813-bb41ddf201ec"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101008AB003DB5A4D644C9FB3BD19B5C7E000" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="14213891138059eb724b9e737fafccea">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="74a0992f-8328-4daf-870b-3d2b13d3e940" xmlns:ns3="4a37abda-15dd-4e37-8275-3b7fb2897b65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c0714e9ec9c019f03b39320eca5a0ecc" ns2:_="" ns3:_="">
+    <xsd:import namespace="74a0992f-8328-4daf-870b-3d2b13d3e940"/>
+    <xsd:import namespace="4a37abda-15dd-4e37-8275-3b7fb2897b65"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -5379,13 +5379,13 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -5393,7 +5393,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8dbf7540-46e2-4291-999e-80d6200bae7a" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="74a0992f-8328-4daf-870b-3d2b13d3e940" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -5411,45 +5411,45 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e6619b5c-6674-40b7-9c01-33e12ba1bd7c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e6619b5c-6674-40b7-9c01-33e12ba1bd7c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2d13a9ec-4dcc-4bf0-b813-bb41ddf201ec" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4a37abda-15dd-4e37-8275-3b7fb2897b65" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{971d825a-e5a3-48fe-8a61-8f749001443e}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2d13a9ec-4dcc-4bf0-b813-bb41ddf201ec">
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f2a2e70a-4904-448e-b588-7989bbdb9dd5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4a37abda-15dd-4e37-8275-3b7fb2897b65">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -5470,8 +5470,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -5569,5 +5569,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4278381B-F68C-48B9-9D4F-AC9DE20C1517}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E49AC029-473B-4874-8B26-4C51CE2DAD68}"/>
 </file>